--- a/public/sap-reporting/expansion-150-downloads/EXT-CO18-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-CO18-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rccccbcc753834325"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R721fa4bd7d314de8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R1dd6406f2a9b42fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R1c37d65e06d346b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R92f4d9cc56834ca8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rb7e4d5861e2a48ef"/>
   </x:sheets>
 </x:workbook>
 </file>
